--- a/data/stx_xlsx/NOTE.ST.xlsx
+++ b/data/stx_xlsx/NOTE.ST.xlsx
@@ -13396,13 +13396,19 @@
       <c r="O94" s="19">
         <v>84.13</v>
       </c>
-      <c r="P94" s="18"/>
-      <c r="Q94" s="18"/>
+      <c r="P94" s="19">
+        <v>1.46</v>
+      </c>
+      <c r="Q94" s="19">
+        <v>2.18</v>
+      </c>
       <c r="R94" s="18"/>
       <c r="S94" s="18"/>
       <c r="T94" s="18"/>
       <c r="U94" s="18"/>
-      <c r="V94" s="18"/>
+      <c r="V94" s="19">
+        <v>9.22</v>
+      </c>
       <c r="W94" s="18"/>
     </row>
     <row r="95" ht="15.0" customHeight="1">
